--- a/49849_Intercuenca_Alto_Huallaga/_raw_reportes_xlsx/IDConfig_67611_completo.xlsx
+++ b/49849_Intercuenca_Alto_Huallaga/_raw_reportes_xlsx/IDConfig_67611_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rf1f5b749a38e4038"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R61886f661f6d4e74"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     94.9490</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     65.0247</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     82.0920</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    139.0395</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    107.2192</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     76.1139</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     76.1139</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    104.5077</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     59.9000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>

--- a/49849_Intercuenca_Alto_Huallaga/_raw_reportes_xlsx/IDConfig_67611_completo.xlsx
+++ b/49849_Intercuenca_Alto_Huallaga/_raw_reportes_xlsx/IDConfig_67611_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R61886f661f6d4e74"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Ra6381c015d0a424c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     82.0920</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.5229</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     96.6427</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     71.8218</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     72.5259</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     85.1924</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     80.5698</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    101.8414</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     98.3559</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    189.3627</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    293.6979</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     86.7708</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    105.4065</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    310.5792</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     73.2345</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     89.9845</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     77.5809</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    128.5144</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    221.3474</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     77.5809</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     96.6427</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    152.3922</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    186.7337</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    208.4436</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    211.2675</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    166.5541</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    168.9947</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     55.0460</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     61.1555</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     70.4271</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     89.9845</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    152.3922</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     80.5698</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.3681</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     69.0501</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.3681</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     76.1139</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     59.9000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     53.2942</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     55.0460</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     55.6382</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     57.4396</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     59.9000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     63.7177</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     77.5809</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    114.6728</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    161.7422</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     79.0661</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
@@ -279,7 +999,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     65.0247</x:v>
+        <x:v>     66.3490</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -294,7 +1014,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     82.0920</x:v>
+        <x:v>     83.6328</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -309,7 +1029,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    139.0395</x:v>
+        <x:v>    141.2097</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -324,7 +1044,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    107.2192</x:v>
+        <x:v>    109.0520</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -339,7 +1059,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     76.1139</x:v>
+        <x:v>     77.5809</x:v>
       </x:c>
     </x:row>
     <x:row>
